--- a/demo_output/figure_00_Global inflation — USA, Euroområdet, UK og Ki.xlsx
+++ b/demo_output/figure_00_Global inflation — USA, Euroområdet, UK og Ki.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Euroområdet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kina" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USA inflation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Euroområdet inflation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UK inflation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kina inflation" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>USA inflation</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Euroområdet</t>
+          <t>Euroområdet inflation</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>UK inflation</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Kina</t>
+          <t>Kina inflation</t>
         </is>
       </c>
     </row>
